--- a/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64388</t>
+          <t>65266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80377</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77117</t>
+          <t>77950</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93203</t>
+          <t>93671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148002</t>
+          <t>147863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169584</t>
+          <t>170128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>39943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41172</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53915</t>
+          <t>53371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75497</t>
+          <t>75636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80552</t>
+          <t>80427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96068</t>
+          <t>95870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93035</t>
+          <t>92660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109920</t>
+          <t>109383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178890</t>
+          <t>179419</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202287</t>
+          <t>201641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>44538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47707</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>64066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86817</t>
+          <t>86288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62510</t>
+          <t>62105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77509</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65964</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82010</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130719</t>
+          <t>132268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154203</t>
+          <t>152877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>45743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>46573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66217</t>
+          <t>67543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89701</t>
+          <t>88152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109216</t>
+          <t>109719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128277</t>
+          <t>128820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91629</t>
+          <t>91700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111255</t>
+          <t>111354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206375</t>
+          <t>207207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235602</t>
+          <t>235200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37059</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>55617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>45592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65317</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86680</t>
+          <t>87082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115907</t>
+          <t>115075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>334656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>366650</t>
+          <t>367316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>346609</t>
+          <t>346730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>381488</t>
+          <t>380608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>691673</t>
+          <t>689538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>741191</t>
+          <t>738597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136709</t>
+          <t>136043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169959</t>
+          <t>168703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147061</t>
+          <t>147941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>181940</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>290717</t>
+          <t>293311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340235</t>
+          <t>342370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80909</t>
+          <t>81512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91678</t>
+          <t>91870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>88433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>101174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174461</t>
+          <t>173956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191078</t>
+          <t>190053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>24068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35168</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111510</t>
+          <t>111145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121499</t>
+          <t>121603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>127289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139891</t>
+          <t>140427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241397</t>
+          <t>242689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258837</t>
+          <t>259344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28216</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24702</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42142</t>
+          <t>40850</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87743</t>
+          <t>88393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97749</t>
+          <t>97948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101126</t>
+          <t>100681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110602</t>
+          <t>110350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192142</t>
+          <t>192712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206300</t>
+          <t>206198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123678</t>
+          <t>124140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136673</t>
+          <t>136346</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129544</t>
+          <t>129424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143161</t>
+          <t>143407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258256</t>
+          <t>257957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275911</t>
+          <t>276772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22324</t>
+          <t>21862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25032</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42687</t>
+          <t>42986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>417091</t>
+          <t>418324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>439171</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>459598</t>
+          <t>461494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>485395</t>
+          <t>486339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884960</t>
+          <t>884572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>917749</t>
+          <t>918467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59874</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97997</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>131174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56586</t>
+          <t>55941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>70654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74200</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88222</t>
+          <t>88430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134709</t>
+          <t>135395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154738</t>
+          <t>156138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33499</t>
+          <t>34144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>59364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104041</t>
+          <t>105178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>121531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131901</t>
+          <t>132356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148347</t>
+          <t>148581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241756</t>
+          <t>242427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>265694</t>
+          <t>266191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29811</t>
+          <t>30396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>46749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>26722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43402</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85474</t>
+          <t>84803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74249</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89567</t>
+          <t>89791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85378</t>
+          <t>86028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103047</t>
+          <t>104133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165626</t>
+          <t>166120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188993</t>
+          <t>189454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>26761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47469</t>
+          <t>46819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60406</t>
+          <t>59945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83773</t>
+          <t>83279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112889</t>
+          <t>112404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133498</t>
+          <t>133289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103716</t>
+          <t>104534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123478</t>
+          <t>123162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223764</t>
+          <t>223195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250104</t>
+          <t>250392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53938</t>
+          <t>54423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54492</t>
+          <t>53674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74931</t>
+          <t>74643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101271</t>
+          <t>101840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>365828</t>
+          <t>367557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>399645</t>
+          <t>401043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415346</t>
+          <t>413730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>448830</t>
+          <t>448105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>792992</t>
+          <t>791295</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>837837</t>
+          <t>838073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>124347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>157833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122203</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155687</t>
+          <t>157303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258586</t>
+          <t>258350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>305128</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31565</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>47788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>38963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71595</t>
+          <t>73792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76203</t>
+          <t>76519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>115002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85715</t>
+          <t>85967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68817</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100741</t>
+          <t>101449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141966</t>
+          <t>142691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181490</t>
+          <t>181174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>59655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87501</t>
+          <t>86519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92952</t>
+          <t>94729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122903</t>
+          <t>124008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>160690</t>
+          <t>161138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200224</t>
+          <t>200747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103011</t>
+          <t>103993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129798</t>
+          <t>130857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132132</t>
+          <t>131027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162083</t>
+          <t>160306</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>245324</t>
+          <t>244801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284858</t>
+          <t>284410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>54950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88487</t>
+          <t>89348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141543</t>
+          <t>140586</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166789</t>
+          <t>168989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136319</t>
+          <t>139023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157686</t>
+          <t>157716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287200</t>
+          <t>286339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321258</t>
+          <t>320737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39463</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42525</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64634</t>
+          <t>65300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>89261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116914</t>
+          <t>117653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108142</t>
+          <t>107526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128499</t>
+          <t>127704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116604</t>
+          <t>115938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138713</t>
+          <t>137558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232287</t>
+          <t>231548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261204</t>
+          <t>259940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>169597</t>
+          <t>169639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>221165</t>
+          <t>220990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>224471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>279996</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410914</t>
+          <t>409924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>491807</t>
+          <t>482981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444990</t>
+          <t>445165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496558</t>
+          <t>496516</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>481976</t>
+          <t>478930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534524</t>
+          <t>537501</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>936320</t>
+          <t>945146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017213</t>
+          <t>1018203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77810</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>93649</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>65,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>72947</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65266</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80504</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64624</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>79804</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>69,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>77950</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>93671</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>72,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147863</t>
+          <t>146533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170128</t>
+          <t>169287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -841,67 +841,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>32163</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24640</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40479</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>32262</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24705</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39943</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25405</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>40585</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32163</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24618</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40339</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53371</t>
+          <t>54212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75636</t>
+          <t>76966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>102019</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>93745</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>110520</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>88676</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>80427</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>95870</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>80952</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>96865</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>70,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>102019</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>92660</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>109383</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179419</t>
+          <t>178982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201641</t>
+          <t>202437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38723</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30222</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46997</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36289</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29095</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44538</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28100</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>44013</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>29,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38723</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31359</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48082</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64066</t>
+          <t>63270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86288</t>
+          <t>86725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73793</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65494</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81435</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69834</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62105</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77568</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61975</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>77228</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>64,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>73793</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>66000</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>81457</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132268</t>
+          <t>133683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152877</t>
+          <t>154097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38780</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31138</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>47079</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30280</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45743</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>30620</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>45873</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,25%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38780</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>31116</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46573</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67543</t>
+          <t>66323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88152</t>
+          <t>86737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>101883</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>91390</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>111566</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>119272</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>109719</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>128820</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>110473</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>129442</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>72,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>66,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>101883</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>91700</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>111354</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207207</t>
+          <t>208030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235200</t>
+          <t>232520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55063</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45380</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65556</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46064</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36516</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55617</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35894</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>54863</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>55063</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>45592</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>65246</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87082</t>
+          <t>89762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115075</t>
+          <t>114252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>345138</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>379567</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>334656</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>367316</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>333008</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>365889</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>72,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>346730</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>380608</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>689538</t>
+          <t>692115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>738597</t>
+          <t>737936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>164728</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>148982</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>183411</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>152628</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>136043</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>168703</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>137470</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>164728</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>147941</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>181819</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>293972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342370</t>
+          <t>339793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>95670</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>87673</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>101065</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>87401</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>81512</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91870</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>81033</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>91623</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>83,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>95670</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>88433</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>101174</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173956</t>
+          <t>174008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190053</t>
+          <t>190456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,85%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11436</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24828</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9728</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15617</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5506</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16096</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16831</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11327</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24068</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19576</t>
+          <t>19173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>134319</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>126147</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>140171</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>86,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>117117</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>111145</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>121603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>111293</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>121904</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>90,8%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>134319</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>140427</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>86,91%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242689</t>
+          <t>241914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259344</t>
+          <t>259109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14385</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28409</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11866</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7380</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17838</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7079</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17690</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>9,2%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20237</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14129</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>27267</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>13,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40850</t>
+          <t>41625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,74 +3356,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>106272</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100587</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>110498</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>93772</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88393</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97948</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88112</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97952</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>89,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>84,04%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>93,42%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>106272</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>100681</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>110350</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>307</t>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192712</t>
+          <t>192955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206198</t>
+          <t>206048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10512</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6286</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16197</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11079</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6903</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16458</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6899</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16739</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>6,58%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10512</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>16103</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>137386</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>129493</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>143796</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>130649</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>124140</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>136346</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>123468</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>136209</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>89,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>85,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>93,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>137386</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>129424</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>143407</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>257957</t>
+          <t>258070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>276772</t>
+          <t>276089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17555</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15353</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9656</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21862</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9793</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22534</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17555</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>11534</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>25517</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24171</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>42873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>460235</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>484394</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>418324</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>438557</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>416621</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>438190</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>461494</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>486339</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>884572</t>
+          <t>886523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>918467</t>
+          <t>919393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65136</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>54387</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>78546</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>48026</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38408</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58641</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38775</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>60344</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>65136</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52442</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>77287</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>96353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131174</t>
+          <t>129223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81723</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>73396</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>87804</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>78,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>63948</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55941</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70654</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>56106</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>70938</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81723</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>73768</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>88430</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>78,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135395</t>
+          <t>133828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156138</t>
+          <t>155305</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22951</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16870</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31278</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26137</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19431</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34144</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19147</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33979</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22951</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16244</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30906</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38621</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59364</t>
+          <t>60931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>140807</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>131788</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>149185</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>113491</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>105178</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>121531</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>103948</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>120903</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>74,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>140807</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>132356</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>148581</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242427</t>
+          <t>241924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266191</t>
+          <t>265471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26118</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43515</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>38436</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30396</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46749</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31024</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47979</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>25,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>34496</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>42947</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>61759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84803</t>
+          <t>85306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95183</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86094</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>103069</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82684</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>74765</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89791</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>74145</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90397</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>77,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>95183</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>86028</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>104133</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>71,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166120</t>
+          <t>165407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189454</t>
+          <t>189275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -5421,67 +5421,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>37664</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29778</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46753</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>33868</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26761</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>41787</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>42407</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37664</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28714</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46819</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>60124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83279</t>
+          <t>83992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>114135</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>104352</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>122922</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>72,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>123519</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>112404</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>133289</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>113110</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>132104</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>74,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>114135</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>104534</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>123162</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223195</t>
+          <t>222522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250392</t>
+          <t>249555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44073</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35286</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53856</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>43308</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33538</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>54423</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34723</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>53717</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>44073</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35046</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>53674</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>27,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74643</t>
+          <t>75480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101840</t>
+          <t>102513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>415584</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>449887</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>72,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>367557</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>401043</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>366597</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>400140</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>413730</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>448105</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>791295</t>
+          <t>791620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>838073</t>
+          <t>840951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139183</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121146</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155449</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>141748</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>124347</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>157833</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>125250</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>158793</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139183</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122928</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>157303</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258350</t>
+          <t>255472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305128</t>
+          <t>304803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>48536</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37718</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66714</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>39156</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31313</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47788</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73792</t>
+          <t>49186</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>88912</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76519</t>
+          <t>75132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115002</t>
+          <t>106161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>77370</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59192</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88188</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,04%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>78124</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69492</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>85967</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>66,61%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>73,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66620</t>
+          <t>71885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>101449</t>
+          <t>88438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>166196</t>
+          <t>158065</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>140816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181174</t>
+          <t>171845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103632</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>89392</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>118631</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>72092</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>59655</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>86519</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108746</t>
+          <t>67137</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94729</t>
+          <t>56519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124008</t>
+          <t>78971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>180838</t>
+          <t>170768</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161138</t>
+          <t>152822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200747</t>
+          <t>188536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>133574</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>147814</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>62,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>118420</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103993</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130857</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146289</t>
+          <t>117276</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131027</t>
+          <t>105442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160306</t>
+          <t>127894</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>264710</t>
+          <t>250851</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244801</t>
+          <t>233083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284410</t>
+          <t>268797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>25318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49815</t>
+          <t>43955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>46197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54950</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89348</t>
+          <t>85438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133872</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124386</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>143023</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>153312</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140586</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>168989</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>80,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,84%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148596</t>
+          <t>120052</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139023</t>
+          <t>110853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157716</t>
+          <t>129081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>301908</t>
+          <t>253924</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286339</t>
+          <t>239953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320737</t>
+          <t>266661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>50730</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>40077</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61049</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49456</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40258</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>60436</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53267</t>
+          <t>50471</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>41989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65300</t>
+          <t>62505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102724</t>
+          <t>101201</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89261</t>
+          <t>86678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117653</t>
+          <t>115734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118646</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108327</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>129299</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>118506</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107526</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>127704</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,56%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>127971</t>
+          <t>116674</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115938</t>
+          <t>104640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137558</t>
+          <t>125156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>246477</t>
+          <t>235320</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>231548</t>
+          <t>220787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>259940</t>
+          <t>249843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>214504</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>264437</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>169639</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>220990</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224471</t>
+          <t>176518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283042</t>
+          <t>214951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409924</t>
+          <t>400997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>482981</t>
+          <t>461688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>463463</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>436392</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>486325</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,13%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>468363</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>445165</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>496516</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>70,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>510927</t>
+          <t>434697</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>414727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>537501</t>
+          <t>453160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>979290</t>
+          <t>898160</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>945146</t>
+          <t>868820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1018203</t>
+          <t>929511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
